--- a/ig/DM-OCTOBRE-2024/CodeSystem-TRE-R212-Equipement.xlsx
+++ b/ig/DM-OCTOBRE-2024/CodeSystem-TRE-R212-Equipement.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="506">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -790,12 +790,18 @@
     <t>Assistant robotisé à la marche</t>
   </si>
   <si>
+    <t>Exosquelette d'aide à la marche</t>
+  </si>
+  <si>
     <t>104</t>
   </si>
   <si>
     <t>Assistant robotisé des membres supérieurs et de la préhension</t>
   </si>
   <si>
+    <t>Exosquelette d'assistance motorisé pour les membres supérieurs</t>
+  </si>
+  <si>
     <t>105</t>
   </si>
   <si>
@@ -808,6 +814,9 @@
     <t>Laboratoire d'analyse tridimensionnelle du mouvement, de la marche</t>
   </si>
   <si>
+    <t>Analyse cinétique, cinématique et électromyographique du mouvement</t>
+  </si>
+  <si>
     <t>107</t>
   </si>
   <si>
@@ -823,7 +832,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>Equipement adapté à l'obésité massive (&lt; 180 kg)</t>
+    <t>Equipement de rééducation adapté à l'obésité</t>
   </si>
   <si>
     <t>110</t>
@@ -868,6 +877,9 @@
     <t>Appartement pour mise en situation d'autonomie</t>
   </si>
   <si>
+    <t>Structure disposant d'appartements qui permettent de tester les capacités d'autonomie d'une personne en situation de dépendance.</t>
+  </si>
+  <si>
     <t>117</t>
   </si>
   <si>
@@ -929,6 +941,9 @@
   </si>
   <si>
     <t>Cuisine thérapeutique et éducative</t>
+  </si>
+  <si>
+    <t>Cuisine ayant les meubles de différentes tailles ou à niveau variable, adaptés aux déficiences et incapacités des patients</t>
   </si>
   <si>
     <t>127</t>
@@ -3145,29 +3160,33 @@
       <c r="C104" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="D104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>258</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="D105" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="D105" t="s" s="2">
+        <v>261</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D106" s="2"/>
     </row>
@@ -3176,22 +3195,24 @@
         <v>49</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="D107" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="D107" t="s" s="2">
+        <v>266</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D108" s="2"/>
     </row>
@@ -3200,10 +3221,10 @@
         <v>49</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D109" s="2"/>
     </row>
@@ -3212,10 +3233,10 @@
         <v>49</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D110" s="2"/>
     </row>
@@ -3224,10 +3245,10 @@
         <v>49</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D111" s="2"/>
     </row>
@@ -3236,10 +3257,10 @@
         <v>49</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D112" s="2"/>
     </row>
@@ -3248,10 +3269,10 @@
         <v>49</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D113" s="2"/>
     </row>
@@ -3260,10 +3281,10 @@
         <v>49</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D114" s="2"/>
     </row>
@@ -3272,10 +3293,10 @@
         <v>49</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D115" s="2"/>
     </row>
@@ -3284,10 +3305,10 @@
         <v>49</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D116" s="2"/>
     </row>
@@ -3296,22 +3317,24 @@
         <v>49</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="D117" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="D117" t="s" s="2">
+        <v>287</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D118" s="2"/>
     </row>
@@ -3320,10 +3343,10 @@
         <v>49</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D119" s="2"/>
     </row>
@@ -3332,10 +3355,10 @@
         <v>49</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D120" s="2"/>
     </row>
@@ -3344,10 +3367,10 @@
         <v>49</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D121" s="2"/>
     </row>
@@ -3356,10 +3379,10 @@
         <v>49</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D122" s="2"/>
     </row>
@@ -3368,10 +3391,10 @@
         <v>49</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D123" s="2"/>
     </row>
@@ -3380,10 +3403,10 @@
         <v>49</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D124" s="2"/>
     </row>
@@ -3392,10 +3415,10 @@
         <v>49</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D125" s="2"/>
     </row>
@@ -3404,13 +3427,13 @@
         <v>49</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="127">
@@ -3418,22 +3441,24 @@
         <v>49</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="D127" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="D127" t="s" s="2">
+        <v>309</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D128" s="2"/>
     </row>
@@ -3442,13 +3467,13 @@
         <v>49</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D129" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="130">
@@ -3456,10 +3481,10 @@
         <v>49</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D130" s="2"/>
     </row>
@@ -3468,10 +3493,10 @@
         <v>49</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D131" s="2"/>
     </row>
@@ -3480,10 +3505,10 @@
         <v>49</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D132" s="2"/>
     </row>
@@ -3492,10 +3517,10 @@
         <v>49</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D133" s="2"/>
     </row>
@@ -3504,10 +3529,10 @@
         <v>49</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D134" s="2"/>
     </row>
@@ -3516,10 +3541,10 @@
         <v>49</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D135" s="2"/>
     </row>
@@ -3528,10 +3553,10 @@
         <v>49</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D136" s="2"/>
     </row>
@@ -3540,10 +3565,10 @@
         <v>49</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D137" s="2"/>
     </row>
@@ -3552,10 +3577,10 @@
         <v>49</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="D138" s="2"/>
     </row>
@@ -3564,10 +3589,10 @@
         <v>49</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D139" s="2"/>
     </row>
@@ -3576,10 +3601,10 @@
         <v>49</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D140" s="2"/>
     </row>
@@ -3588,10 +3613,10 @@
         <v>49</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="D141" s="2"/>
     </row>
@@ -3600,10 +3625,10 @@
         <v>49</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D142" s="2"/>
     </row>
@@ -3612,10 +3637,10 @@
         <v>49</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D143" s="2"/>
     </row>
@@ -3624,10 +3649,10 @@
         <v>49</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="D144" s="2"/>
     </row>
@@ -3636,10 +3661,10 @@
         <v>49</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D145" s="2"/>
     </row>
@@ -3648,10 +3673,10 @@
         <v>49</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="D146" s="2"/>
     </row>
@@ -3660,10 +3685,10 @@
         <v>49</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D147" s="2"/>
     </row>
@@ -3672,10 +3697,10 @@
         <v>49</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D148" s="2"/>
     </row>
@@ -3684,13 +3709,13 @@
         <v>49</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="D149" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="150">
@@ -3698,10 +3723,10 @@
         <v>49</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="D150" s="2"/>
     </row>
@@ -3710,10 +3735,10 @@
         <v>49</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D151" s="2"/>
     </row>
@@ -3722,10 +3747,10 @@
         <v>49</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D152" s="2"/>
     </row>
@@ -3734,10 +3759,10 @@
         <v>49</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="D153" s="2"/>
     </row>
@@ -3746,10 +3771,10 @@
         <v>49</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D154" s="2"/>
     </row>
@@ -3758,10 +3783,10 @@
         <v>49</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D155" s="2"/>
     </row>
@@ -3770,10 +3795,10 @@
         <v>49</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D156" s="2"/>
     </row>
@@ -3782,10 +3807,10 @@
         <v>49</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D157" s="2"/>
     </row>
@@ -3794,10 +3819,10 @@
         <v>49</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D158" s="2"/>
     </row>
@@ -3806,10 +3831,10 @@
         <v>49</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D159" s="2"/>
     </row>
@@ -3818,10 +3843,10 @@
         <v>49</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D160" s="2"/>
     </row>
@@ -3830,10 +3855,10 @@
         <v>49</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="D161" s="2"/>
     </row>
@@ -3842,10 +3867,10 @@
         <v>49</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D162" s="2"/>
     </row>
@@ -3854,10 +3879,10 @@
         <v>49</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D163" s="2"/>
     </row>
@@ -3866,10 +3891,10 @@
         <v>49</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="D164" s="2"/>
     </row>
@@ -3878,10 +3903,10 @@
         <v>49</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D165" s="2"/>
     </row>
@@ -3890,10 +3915,10 @@
         <v>49</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D166" s="2"/>
     </row>
@@ -3902,10 +3927,10 @@
         <v>49</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="D167" s="2"/>
     </row>
@@ -3914,10 +3939,10 @@
         <v>49</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D168" s="2"/>
     </row>
@@ -3926,10 +3951,10 @@
         <v>49</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D169" s="2"/>
     </row>
@@ -3938,10 +3963,10 @@
         <v>49</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="D170" s="2"/>
     </row>
@@ -3950,10 +3975,10 @@
         <v>49</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D171" s="2"/>
     </row>
@@ -3962,10 +3987,10 @@
         <v>49</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="D172" s="2"/>
     </row>
@@ -3974,10 +3999,10 @@
         <v>49</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="D173" s="2"/>
     </row>
@@ -3986,10 +4011,10 @@
         <v>49</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D174" s="2"/>
     </row>
@@ -3998,10 +4023,10 @@
         <v>49</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D175" s="2"/>
     </row>
@@ -4010,10 +4035,10 @@
         <v>49</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D176" s="2"/>
     </row>
@@ -4022,10 +4047,10 @@
         <v>49</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D177" s="2"/>
     </row>
@@ -4034,10 +4059,10 @@
         <v>49</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D178" s="2"/>
     </row>
@@ -4046,10 +4071,10 @@
         <v>49</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="D179" s="2"/>
     </row>
@@ -4058,10 +4083,10 @@
         <v>49</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D180" s="2"/>
     </row>
@@ -4070,10 +4095,10 @@
         <v>49</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D181" s="2"/>
     </row>
@@ -4082,10 +4107,10 @@
         <v>49</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D182" s="2"/>
     </row>
@@ -4094,10 +4119,10 @@
         <v>49</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D183" s="2"/>
     </row>
@@ -4106,10 +4131,10 @@
         <v>49</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D184" s="2"/>
     </row>
@@ -4118,10 +4143,10 @@
         <v>49</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D185" s="2"/>
     </row>
@@ -4130,10 +4155,10 @@
         <v>49</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D186" s="2"/>
     </row>
@@ -4142,10 +4167,10 @@
         <v>49</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D187" s="2"/>
     </row>
@@ -4154,10 +4179,10 @@
         <v>49</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D188" s="2"/>
     </row>
@@ -4166,10 +4191,10 @@
         <v>49</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D189" s="2"/>
     </row>
@@ -4178,10 +4203,10 @@
         <v>49</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D190" s="2"/>
     </row>
@@ -4190,10 +4215,10 @@
         <v>49</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="D191" s="2"/>
     </row>
@@ -4202,10 +4227,10 @@
         <v>49</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="D192" s="2"/>
     </row>
@@ -4214,13 +4239,13 @@
         <v>49</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D193" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="194">
@@ -4228,10 +4253,10 @@
         <v>49</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D194" s="2"/>
     </row>
@@ -4240,10 +4265,10 @@
         <v>49</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D195" s="2"/>
     </row>
@@ -4252,10 +4277,10 @@
         <v>49</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="D196" s="2"/>
     </row>
@@ -4264,10 +4289,10 @@
         <v>49</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D197" s="2"/>
     </row>
@@ -4276,10 +4301,10 @@
         <v>49</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D198" s="2"/>
     </row>
@@ -4288,10 +4313,10 @@
         <v>49</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="D199" s="2"/>
     </row>
@@ -4300,13 +4325,13 @@
         <v>49</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D200" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="201">
@@ -4314,13 +4339,13 @@
         <v>49</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D201" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="202">
@@ -4328,13 +4353,13 @@
         <v>49</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D202" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203">
@@ -4342,13 +4367,13 @@
         <v>49</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="D203" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204">
@@ -4356,13 +4381,13 @@
         <v>49</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D204" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205">
@@ -4370,10 +4395,10 @@
         <v>49</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="D205" s="2"/>
     </row>
@@ -4382,10 +4407,10 @@
         <v>49</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D206" s="2"/>
     </row>
@@ -4394,10 +4419,10 @@
         <v>49</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D207" s="2"/>
     </row>
@@ -4406,10 +4431,10 @@
         <v>49</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -4418,10 +4443,10 @@
         <v>49</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -4430,10 +4455,10 @@
         <v>49</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -4442,10 +4467,10 @@
         <v>49</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D211" s="2"/>
     </row>
@@ -4454,10 +4479,10 @@
         <v>49</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="D212" s="2"/>
     </row>
@@ -4466,10 +4491,10 @@
         <v>49</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="D213" s="2"/>
     </row>
@@ -4478,10 +4503,10 @@
         <v>49</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -4490,10 +4515,10 @@
         <v>49</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -4502,10 +4527,10 @@
         <v>49</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -4514,10 +4539,10 @@
         <v>49</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D217" s="2"/>
     </row>
@@ -4526,10 +4551,10 @@
         <v>49</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D218" s="2"/>
     </row>
@@ -4538,10 +4563,10 @@
         <v>49</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D219" s="2"/>
     </row>
@@ -4550,10 +4575,10 @@
         <v>49</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="D220" s="2"/>
     </row>
@@ -4562,10 +4587,10 @@
         <v>49</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="D221" s="2"/>
     </row>
